--- a/logs/experiment_log.xlsx
+++ b/logs/experiment_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0051rra\Downloads\Neurofind Project\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B253E0E-913A-4C5F-A85E-0318D3210F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2107E2F2-58DD-49F2-90E7-EBAC2B492777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31065" yWindow="660" windowWidth="21600" windowHeight="12645" xr2:uid="{F9776EC4-E5BF-4E5D-8A0A-73F1CB30A0CB}"/>
+    <workbookView xWindow="11790" yWindow="10800" windowWidth="19420" windowHeight="10300" xr2:uid="{F9776EC4-E5BF-4E5D-8A0A-73F1CB30A0CB}"/>
   </bookViews>
   <sheets>
     <sheet name="experiments_log" sheetId="1" r:id="rId1"/>
@@ -20,63 +20,65 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>experiment_id</t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>hypothesis</t>
-  </si>
-  <si>
-    <t>query_stack</t>
-  </si>
-  <si>
-    <t>target_stack</t>
-  </si>
-  <si>
-    <t>query_id</t>
-  </si>
-  <si>
-    <t>query_z</t>
-  </si>
-  <si>
-    <t>query_y</t>
-  </si>
-  <si>
-    <t>query_x</t>
-  </si>
-  <si>
-    <t>search_strategy</t>
-  </si>
-  <si>
-    <t>search_radius</t>
-  </si>
-  <si>
-    <t>candidate_selection</t>
-  </si>
-  <si>
-    <t>pred_z</t>
-  </si>
-  <si>
-    <t>pred_y</t>
-  </si>
-  <si>
-    <t>pred_x</t>
-  </si>
-  <si>
-    <t>accuracy</t>
-  </si>
-  <si>
-    <t>runtime_seconds</t>
-  </si>
-  <si>
-    <t>num_candidates</t>
-  </si>
-  <si>
-    <t>notes</t>
+    <t>Ex1</t>
+  </si>
+  <si>
+    <t>12.06.2026</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>number_of_candidates_searched; 
+runtime_seconds;
+distance_to_target;</t>
+  </si>
+  <si>
+    <t>Evaluate full search vs local search using human-labeled stack1 and stack2 frame-0 pairs</t>
+  </si>
+  <si>
+    <t>15  label pairs;
+stack2 test candidate points;
+stack2 test embeddings;
+test size = 1000</t>
+  </si>
+  <si>
+    <t>Ex1_local_search_results_stack1_stack2_test.csv</t>
+  </si>
+  <si>
+    <t>Pipeline runs on label pairs; predictions are far from target in given subset.</t>
+  </si>
+  <si>
+    <t>Uses only first 1000 stack2 candidates and embeddings and not full candidate set, results are for pipeline validation.</t>
   </si>
 </sst>
 </file>
@@ -560,10 +562,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -940,88 +948,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DFB3CA-602B-465D-B2C4-A0AAF5DCABFC}">
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
-    <col min="12" max="12" width="18.7109375" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" customWidth="1"/>
-    <col min="18" max="18" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" customWidth="1"/>
+    <col min="3" max="3" width="36.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24.08984375" customWidth="1"/>
+    <col min="5" max="5" width="33.6328125" customWidth="1"/>
+    <col min="6" max="6" width="29.90625" customWidth="1"/>
+    <col min="7" max="7" width="24.6328125" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="26.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/logs/experiment_log.xlsx
+++ b/logs/experiment_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0051rra\Downloads\Neurofind Project\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2107E2F2-58DD-49F2-90E7-EBAC2B492777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF39A04-527D-4311-9AD1-52E6F349E298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11790" yWindow="10800" windowWidth="19420" windowHeight="10300" xr2:uid="{F9776EC4-E5BF-4E5D-8A0A-73F1CB30A0CB}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" xr2:uid="{F9776EC4-E5BF-4E5D-8A0A-73F1CB30A0CB}"/>
   </bookViews>
   <sheets>
     <sheet name="experiments_log" sheetId="1" r:id="rId1"/>
@@ -20,67 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>experiment_id</t>
-  </si>
-  <si>
-    <t>Ex1</t>
-  </si>
-  <si>
-    <t>12.06.2026</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>number_of_candidates_searched; 
-runtime_seconds;
-distance_to_target;</t>
-  </si>
-  <si>
-    <t>Evaluate full search vs local search using human-labeled stack1 and stack2 frame-0 pairs</t>
-  </si>
-  <si>
-    <t>15  label pairs;
-stack2 test candidate points;
-stack2 test embeddings;
-test size = 1000</t>
-  </si>
-  <si>
-    <t>Ex1_local_search_results_stack1_stack2_test.csv</t>
-  </si>
-  <si>
-    <t>Pipeline runs on label pairs; predictions are far from target in given subset.</t>
-  </si>
-  <si>
-    <t>Uses only first 1000 stack2 candidates and embeddings and not full candidate set, results are for pipeline validation.</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -562,14 +502,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -948,79 +882,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DFB3CA-602B-465D-B2C4-A0AAF5DCABFC}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" customWidth="1"/>
-    <col min="3" max="3" width="36.453125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24.08984375" customWidth="1"/>
-    <col min="5" max="5" width="33.6328125" customWidth="1"/>
-    <col min="6" max="6" width="29.90625" customWidth="1"/>
-    <col min="7" max="7" width="24.6328125" customWidth="1"/>
-    <col min="8" max="8" width="17.26953125" customWidth="1"/>
-    <col min="9" max="9" width="26.54296875" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="5" max="5" width="33.5703125" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/logs/experiment_log.xlsx
+++ b/logs/experiment_log.xlsx
@@ -8,24 +8,176 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0051rra\Downloads\Neurofind Project\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF39A04-527D-4311-9AD1-52E6F349E298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2013732-DF37-4461-81F2-06D610D0FBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" xr2:uid="{F9776EC4-E5BF-4E5D-8A0A-73F1CB30A0CB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F9776EC4-E5BF-4E5D-8A0A-73F1CB30A0CB}"/>
   </bookViews>
   <sheets>
-    <sheet name="experiments_log" sheetId="1" r:id="rId1"/>
+    <sheet name="H1 Log" sheetId="1" r:id="rId1"/>
+    <sheet name="H2 Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="36">
+  <si>
+    <t>Each row = the average across all tracks for one strategy, in one stack's one frame pair.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Example: the row A1, frame 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Innomotics Haffer"/>
+        <family val="2"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1, euclidean 25% shows 14525, this is the average number of candidates searched across all 19 individual spines tracked in the output file.</t>
+    </r>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Frame Pair</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>Area (%)</t>
+  </si>
+  <si>
+    <t>Candidates Searched</t>
+  </si>
+  <si>
+    <t>Error (um)</t>
+  </si>
+  <si>
+    <t>Total Time (s)</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>0-&gt;1</t>
+  </si>
+  <si>
+    <t>full_search</t>
+  </si>
+  <si>
+    <t>euclidean</t>
+  </si>
+  <si>
+    <t>manhattan</t>
+  </si>
+  <si>
+    <t>1-&gt;2</t>
+  </si>
+  <si>
+    <t>2-&gt;3</t>
+  </si>
+  <si>
+    <t>3-&gt;4</t>
+  </si>
+  <si>
+    <t>4-&gt;5</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>No. of Tracks</t>
+  </si>
+  <si>
+    <t>Hypothesis 1 - Local Search</t>
+  </si>
+  <si>
+    <t>Each row = the average across all tracks for one setting, in one stack's one frame pair.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Example: the row A1, frame 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Innomotics Haffer"/>
+        <family val="2"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1, grid size 8x8 shows 2722.63, this is the average number of candidates searched across all 19 individual spines tracked in the output file.</t>
+    </r>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Hit Rate (%)</t>
+  </si>
+  <si>
+    <t>Error on Hits (um)</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>2x2</t>
+  </si>
+  <si>
+    <t>4x4</t>
+  </si>
+  <si>
+    <t>8x8</t>
+  </si>
+  <si>
+    <t>16x16</t>
+  </si>
+  <si>
+    <t>32x32</t>
+  </si>
+  <si>
+    <t>Total number of rows in this sheet = 3 stacks x 5 frame pairs each stack x 6 settings each frame pair (full search + 5 grid sizes) = 90</t>
+  </si>
+  <si>
+    <t>Hypothesis 2 - Grid Search</t>
+  </si>
+  <si>
+    <t>Total number of rows in this sheet = 3 stacks x 5 frame pairs each stack x 5 strategies each frame pair = 75</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,8 +312,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Innomotics Haffer"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,8 +529,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -457,8 +657,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -501,14 +716,29 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="42" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="10" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -546,6 +776,7 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{6F503A93-3AF1-4E73-9B80-A9C30FFF5FDE}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -882,22 +1113,4461 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DFB3CA-602B-465D-B2C4-A0AAF5DCABFC}">
-  <dimension ref="C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I81"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="36.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" customWidth="1"/>
-    <col min="5" max="5" width="33.5703125" customWidth="1"/>
-    <col min="6" max="6" width="29.85546875" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" customWidth="1"/>
+    <col min="3" max="3" width="28.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.54296875" customWidth="1"/>
+    <col min="5" max="5" width="33.54296875" customWidth="1"/>
+    <col min="6" max="6" width="29.81640625" customWidth="1"/>
+    <col min="7" max="7" width="24.54296875" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="26.54296875" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.45">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
+        <v>19</v>
+      </c>
+      <c r="F7" s="6">
+        <v>31172</v>
+      </c>
+      <c r="G7" s="6">
+        <v>14.92</v>
+      </c>
+      <c r="H7" s="6">
+        <v>410.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="6">
+        <v>19</v>
+      </c>
+      <c r="F8" s="6">
+        <v>14525</v>
+      </c>
+      <c r="G8" s="6">
+        <v>8.86</v>
+      </c>
+      <c r="H8" s="6">
+        <v>191.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="6">
+        <v>19</v>
+      </c>
+      <c r="F9" s="6">
+        <v>18449</v>
+      </c>
+      <c r="G9" s="6">
+        <v>10.29</v>
+      </c>
+      <c r="H9" s="6">
+        <v>243.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="6">
+        <v>19</v>
+      </c>
+      <c r="F10" s="6">
+        <v>15455</v>
+      </c>
+      <c r="G10" s="6">
+        <v>10.26</v>
+      </c>
+      <c r="H10" s="6">
+        <v>203.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>19</v>
+      </c>
+      <c r="F11" s="6">
+        <v>19090</v>
+      </c>
+      <c r="G11" s="6">
+        <v>10.32</v>
+      </c>
+      <c r="H11" s="6">
+        <v>251.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
+        <v>17</v>
+      </c>
+      <c r="F12" s="6">
+        <v>34272</v>
+      </c>
+      <c r="G12" s="6">
+        <v>11.35</v>
+      </c>
+      <c r="H12" s="6">
+        <v>451.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="6">
+        <v>17</v>
+      </c>
+      <c r="F13" s="6">
+        <v>16799</v>
+      </c>
+      <c r="G13" s="6">
+        <v>6.26</v>
+      </c>
+      <c r="H13" s="6">
+        <v>221.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E14" s="6">
+        <v>17</v>
+      </c>
+      <c r="F14" s="6">
+        <v>20582</v>
+      </c>
+      <c r="G14" s="6">
+        <v>7.77</v>
+      </c>
+      <c r="H14" s="6">
+        <v>271.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="6">
+        <v>17</v>
+      </c>
+      <c r="F15" s="6">
+        <v>17571</v>
+      </c>
+      <c r="G15" s="6">
+        <v>6.26</v>
+      </c>
+      <c r="H15" s="6">
+        <v>231.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>17</v>
+      </c>
+      <c r="F16" s="6">
+        <v>21233</v>
+      </c>
+      <c r="G16" s="6">
+        <v>7.77</v>
+      </c>
+      <c r="H16" s="6">
+        <v>279.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6">
+        <v>17</v>
+      </c>
+      <c r="F17" s="6">
+        <v>39423</v>
+      </c>
+      <c r="G17" s="6">
+        <v>13.14</v>
+      </c>
+      <c r="H17" s="6">
+        <v>519.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="6">
+        <v>17</v>
+      </c>
+      <c r="F18" s="6">
+        <v>17690</v>
+      </c>
+      <c r="G18" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="H18" s="6">
+        <v>233.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E19" s="6">
+        <v>17</v>
+      </c>
+      <c r="F19" s="6">
+        <v>22436</v>
+      </c>
+      <c r="G19" s="6">
+        <v>9.09</v>
+      </c>
+      <c r="H19" s="6">
+        <v>295.60000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E20" s="6">
+        <v>17</v>
+      </c>
+      <c r="F20" s="6">
+        <v>18581</v>
+      </c>
+      <c r="G20" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="H20" s="6">
+        <v>244.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E21" s="6">
+        <v>17</v>
+      </c>
+      <c r="F21" s="6">
+        <v>23115</v>
+      </c>
+      <c r="G21" s="6">
+        <v>9.09</v>
+      </c>
+      <c r="H21" s="6">
+        <v>304.60000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6">
+        <v>20</v>
+      </c>
+      <c r="F22" s="6">
+        <v>22915</v>
+      </c>
+      <c r="G22" s="6">
+        <v>12.65</v>
+      </c>
+      <c r="H22" s="6">
+        <v>301.89999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="6">
+        <v>20</v>
+      </c>
+      <c r="F23" s="6">
+        <v>11969</v>
+      </c>
+      <c r="G23" s="6">
+        <v>23.59</v>
+      </c>
+      <c r="H23" s="6">
+        <v>157.69999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="6">
+        <v>20</v>
+      </c>
+      <c r="F24" s="6">
+        <v>15476</v>
+      </c>
+      <c r="G24" s="6">
+        <v>11.85</v>
+      </c>
+      <c r="H24" s="6">
+        <v>203.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E25" s="6">
+        <v>20</v>
+      </c>
+      <c r="F25" s="6">
+        <v>12334</v>
+      </c>
+      <c r="G25" s="6">
+        <v>23.14</v>
+      </c>
+      <c r="H25" s="6">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="6">
+        <v>20</v>
+      </c>
+      <c r="F26" s="6">
+        <v>15468</v>
+      </c>
+      <c r="G26" s="6">
+        <v>13.92</v>
+      </c>
+      <c r="H26" s="6">
+        <v>203.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6">
+        <v>23</v>
+      </c>
+      <c r="F27" s="6">
+        <v>28297</v>
+      </c>
+      <c r="G27" s="6">
+        <v>20.53</v>
+      </c>
+      <c r="H27" s="6">
+        <v>372.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E28" s="6">
+        <v>23</v>
+      </c>
+      <c r="F28" s="6">
+        <v>10475</v>
+      </c>
+      <c r="G28" s="6">
+        <v>27.3</v>
+      </c>
+      <c r="H28" s="6">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E29" s="6">
+        <v>23</v>
+      </c>
+      <c r="F29" s="6">
+        <v>13867</v>
+      </c>
+      <c r="G29" s="6">
+        <v>25.51</v>
+      </c>
+      <c r="H29" s="6">
+        <v>182.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E30" s="6">
+        <v>23</v>
+      </c>
+      <c r="F30" s="6">
+        <v>10893</v>
+      </c>
+      <c r="G30" s="6">
+        <v>27.3</v>
+      </c>
+      <c r="H30" s="6">
+        <v>143.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E31" s="6">
+        <v>23</v>
+      </c>
+      <c r="F31" s="6">
+        <v>14039</v>
+      </c>
+      <c r="G31" s="6">
+        <v>24.9</v>
+      </c>
+      <c r="H31" s="6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6">
+        <v>40</v>
+      </c>
+      <c r="F32" s="6">
+        <v>164533</v>
+      </c>
+      <c r="G32" s="6">
+        <v>20.79</v>
+      </c>
+      <c r="H32" s="6">
+        <v>2103.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E33" s="6">
+        <v>40</v>
+      </c>
+      <c r="F33" s="6">
+        <v>61554</v>
+      </c>
+      <c r="G33" s="6">
+        <v>10.59</v>
+      </c>
+      <c r="H33" s="6">
+        <v>786.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E34" s="6">
+        <v>40</v>
+      </c>
+      <c r="F34" s="6">
+        <v>86827</v>
+      </c>
+      <c r="G34" s="6">
+        <v>12.16</v>
+      </c>
+      <c r="H34" s="6">
+        <v>1109.9000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E35" s="6">
+        <v>40</v>
+      </c>
+      <c r="F35" s="6">
+        <v>60778</v>
+      </c>
+      <c r="G35" s="6">
+        <v>10.37</v>
+      </c>
+      <c r="H35" s="6">
+        <v>776.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E36" s="6">
+        <v>40</v>
+      </c>
+      <c r="F36" s="6">
+        <v>85832</v>
+      </c>
+      <c r="G36" s="6">
+        <v>12.16</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1097.0999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6">
+        <v>40</v>
+      </c>
+      <c r="F37" s="6">
+        <v>141581</v>
+      </c>
+      <c r="G37" s="6">
+        <v>19</v>
+      </c>
+      <c r="H37" s="6">
+        <v>1809.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E38" s="6">
+        <v>40</v>
+      </c>
+      <c r="F38" s="6">
+        <v>55614</v>
+      </c>
+      <c r="G38" s="6">
+        <v>8.92</v>
+      </c>
+      <c r="H38" s="6">
+        <v>710.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E39" s="6">
+        <v>40</v>
+      </c>
+      <c r="F39" s="6">
+        <v>78131</v>
+      </c>
+      <c r="G39" s="6">
+        <v>11.37</v>
+      </c>
+      <c r="H39" s="6">
+        <v>998.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E40" s="6">
+        <v>40</v>
+      </c>
+      <c r="F40" s="6">
+        <v>55191</v>
+      </c>
+      <c r="G40" s="6">
+        <v>8.69</v>
+      </c>
+      <c r="H40" s="6">
+        <v>705.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E41" s="6">
+        <v>40</v>
+      </c>
+      <c r="F41" s="6">
+        <v>77397</v>
+      </c>
+      <c r="G41" s="6">
+        <v>11.14</v>
+      </c>
+      <c r="H41" s="6">
+        <v>989.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6">
+        <v>41</v>
+      </c>
+      <c r="F42" s="6">
+        <v>144481</v>
+      </c>
+      <c r="G42" s="6">
+        <v>14.99</v>
+      </c>
+      <c r="H42" s="6">
+        <v>1846.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E43" s="6">
+        <v>41</v>
+      </c>
+      <c r="F43" s="6">
+        <v>58219</v>
+      </c>
+      <c r="G43" s="6">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="H43" s="6">
+        <v>744.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E44" s="6">
+        <v>41</v>
+      </c>
+      <c r="F44" s="6">
+        <v>79809</v>
+      </c>
+      <c r="G44" s="6">
+        <v>10.94</v>
+      </c>
+      <c r="H44" s="6">
+        <v>1020.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E45" s="6">
+        <v>41</v>
+      </c>
+      <c r="F45" s="6">
+        <v>57773</v>
+      </c>
+      <c r="G45" s="6">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="H45" s="6">
+        <v>738.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E46" s="6">
+        <v>41</v>
+      </c>
+      <c r="F46" s="6">
+        <v>78652</v>
+      </c>
+      <c r="G46" s="6">
+        <v>10.54</v>
+      </c>
+      <c r="H46" s="6">
+        <v>1005.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6">
+        <v>41</v>
+      </c>
+      <c r="F47" s="6">
+        <v>162924</v>
+      </c>
+      <c r="G47" s="6">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="H47" s="6">
+        <v>2082.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E48" s="6">
+        <v>41</v>
+      </c>
+      <c r="F48" s="6">
+        <v>68379</v>
+      </c>
+      <c r="G48" s="6">
+        <v>7.35</v>
+      </c>
+      <c r="H48" s="6">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E49" s="6">
+        <v>41</v>
+      </c>
+      <c r="F49" s="6">
+        <v>92212</v>
+      </c>
+      <c r="G49" s="6">
+        <v>11</v>
+      </c>
+      <c r="H49" s="6">
+        <v>1178.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E50" s="6">
+        <v>41</v>
+      </c>
+      <c r="F50" s="6">
+        <v>68098</v>
+      </c>
+      <c r="G50" s="6">
+        <v>8.08</v>
+      </c>
+      <c r="H50" s="6">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E51" s="6">
+        <v>41</v>
+      </c>
+      <c r="F51" s="6">
+        <v>91106</v>
+      </c>
+      <c r="G51" s="6">
+        <v>10.87</v>
+      </c>
+      <c r="H51" s="6">
+        <v>1164.5999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6">
+        <v>43</v>
+      </c>
+      <c r="F52" s="6">
+        <v>165627</v>
+      </c>
+      <c r="G52" s="6">
+        <v>33.4</v>
+      </c>
+      <c r="H52" s="6">
+        <v>2117.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E53" s="6">
+        <v>43</v>
+      </c>
+      <c r="F53" s="6">
+        <v>63826</v>
+      </c>
+      <c r="G53" s="6">
+        <v>13.56</v>
+      </c>
+      <c r="H53" s="6">
+        <v>815.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E54" s="6">
+        <v>43</v>
+      </c>
+      <c r="F54" s="6">
+        <v>86334</v>
+      </c>
+      <c r="G54" s="6">
+        <v>18.13</v>
+      </c>
+      <c r="H54" s="6">
+        <v>1103.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E55" s="6">
+        <v>43</v>
+      </c>
+      <c r="F55" s="6">
+        <v>63915</v>
+      </c>
+      <c r="G55" s="6">
+        <v>14.79</v>
+      </c>
+      <c r="H55" s="6">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E56" s="6">
+        <v>43</v>
+      </c>
+      <c r="F56" s="6">
+        <v>85875</v>
+      </c>
+      <c r="G56" s="6">
+        <v>18.55</v>
+      </c>
+      <c r="H56" s="6">
+        <v>1097.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6">
+        <v>27</v>
+      </c>
+      <c r="F57" s="6">
+        <v>84326</v>
+      </c>
+      <c r="G57" s="6">
+        <v>24.14</v>
+      </c>
+      <c r="H57" s="6">
+        <v>1132.9000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E58" s="6">
+        <v>27</v>
+      </c>
+      <c r="F58" s="6">
+        <v>12990</v>
+      </c>
+      <c r="G58" s="6">
+        <v>10.11</v>
+      </c>
+      <c r="H58" s="6">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E59" s="6">
+        <v>27</v>
+      </c>
+      <c r="F59" s="6">
+        <v>20609</v>
+      </c>
+      <c r="G59" s="6">
+        <v>12.05</v>
+      </c>
+      <c r="H59" s="6">
+        <v>276.89999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E60" s="6">
+        <v>27</v>
+      </c>
+      <c r="F60" s="6">
+        <v>12051</v>
+      </c>
+      <c r="G60" s="6">
+        <v>9.25</v>
+      </c>
+      <c r="H60" s="6">
+        <v>161.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E61" s="6">
+        <v>27</v>
+      </c>
+      <c r="F61" s="6">
+        <v>18718</v>
+      </c>
+      <c r="G61" s="6">
+        <v>11.95</v>
+      </c>
+      <c r="H61" s="6">
+        <v>251.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6">
+        <v>25</v>
+      </c>
+      <c r="F62" s="6">
+        <v>79823</v>
+      </c>
+      <c r="G62" s="6">
+        <v>38.44</v>
+      </c>
+      <c r="H62" s="6">
+        <v>1072.4000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E63" s="6">
+        <v>25</v>
+      </c>
+      <c r="F63" s="6">
+        <v>14343</v>
+      </c>
+      <c r="G63" s="6">
+        <v>12.68</v>
+      </c>
+      <c r="H63" s="6">
+        <v>192.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E64" s="6">
+        <v>25</v>
+      </c>
+      <c r="F64" s="6">
+        <v>21149</v>
+      </c>
+      <c r="G64" s="6">
+        <v>17.77</v>
+      </c>
+      <c r="H64" s="6">
+        <v>284.10000000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E65" s="6">
+        <v>25</v>
+      </c>
+      <c r="F65" s="6">
+        <v>13400</v>
+      </c>
+      <c r="G65" s="6">
+        <v>11.06</v>
+      </c>
+      <c r="H65" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E66" s="6">
+        <v>25</v>
+      </c>
+      <c r="F66" s="6">
+        <v>19272</v>
+      </c>
+      <c r="G66" s="6">
+        <v>17.25</v>
+      </c>
+      <c r="H66" s="6">
+        <v>258.89999999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6">
+        <v>25</v>
+      </c>
+      <c r="F67" s="6">
+        <v>118615</v>
+      </c>
+      <c r="G67" s="6">
+        <v>37.75</v>
+      </c>
+      <c r="H67" s="6">
+        <v>1593.6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E68" s="6">
+        <v>25</v>
+      </c>
+      <c r="F68" s="6">
+        <v>21341</v>
+      </c>
+      <c r="G68" s="6">
+        <v>10.87</v>
+      </c>
+      <c r="H68" s="6">
+        <v>286.7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E69" s="6">
+        <v>25</v>
+      </c>
+      <c r="F69" s="6">
+        <v>32018</v>
+      </c>
+      <c r="G69" s="6">
+        <v>17.7</v>
+      </c>
+      <c r="H69" s="6">
+        <v>430.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E70" s="6">
+        <v>25</v>
+      </c>
+      <c r="F70" s="6">
+        <v>20972</v>
+      </c>
+      <c r="G70" s="6">
+        <v>11.26</v>
+      </c>
+      <c r="H70" s="6">
+        <v>281.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E71" s="6">
+        <v>25</v>
+      </c>
+      <c r="F71" s="6">
+        <v>30649</v>
+      </c>
+      <c r="G71" s="6">
+        <v>18.8</v>
+      </c>
+      <c r="H71" s="6">
+        <v>411.8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6">
+        <v>24</v>
+      </c>
+      <c r="F72" s="6">
+        <v>55778</v>
+      </c>
+      <c r="G72" s="6">
+        <v>21.29</v>
+      </c>
+      <c r="H72" s="6">
+        <v>749.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E73" s="6">
+        <v>24</v>
+      </c>
+      <c r="F73" s="6">
+        <v>8158</v>
+      </c>
+      <c r="G73" s="6">
+        <v>12.18</v>
+      </c>
+      <c r="H73" s="6">
+        <v>109.6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A74" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E74" s="6">
+        <v>24</v>
+      </c>
+      <c r="F74" s="6">
+        <v>15895</v>
+      </c>
+      <c r="G74" s="6">
+        <v>13.93</v>
+      </c>
+      <c r="H74" s="6">
+        <v>213.6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E75" s="6">
+        <v>24</v>
+      </c>
+      <c r="F75" s="6">
+        <v>8089</v>
+      </c>
+      <c r="G75" s="6">
+        <v>10.7</v>
+      </c>
+      <c r="H75" s="6">
+        <v>108.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E76" s="6">
+        <v>24</v>
+      </c>
+      <c r="F76" s="6">
+        <v>15993</v>
+      </c>
+      <c r="G76" s="6">
+        <v>13.28</v>
+      </c>
+      <c r="H76" s="6">
+        <v>214.9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A77" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6">
+        <v>25</v>
+      </c>
+      <c r="F77" s="6">
+        <v>98318</v>
+      </c>
+      <c r="G77" s="6">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="H77" s="6">
+        <v>1320.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E78" s="6">
+        <v>25</v>
+      </c>
+      <c r="F78" s="6">
+        <v>18636</v>
+      </c>
+      <c r="G78" s="6">
+        <v>6.69</v>
+      </c>
+      <c r="H78" s="6">
+        <v>250.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E79" s="6">
+        <v>25</v>
+      </c>
+      <c r="F79" s="6">
+        <v>25194</v>
+      </c>
+      <c r="G79" s="6">
+        <v>7.21</v>
+      </c>
+      <c r="H79" s="6">
+        <v>338.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="E80" s="6">
+        <v>25</v>
+      </c>
+      <c r="F80" s="6">
+        <v>18088</v>
+      </c>
+      <c r="G80" s="6">
+        <v>6.38</v>
+      </c>
+      <c r="H80" s="6">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E81" s="6">
+        <v>25</v>
+      </c>
+      <c r="F81" s="6">
+        <v>24236</v>
+      </c>
+      <c r="G81" s="6">
+        <v>6.69</v>
+      </c>
+      <c r="H81" s="6">
+        <v>325.60000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF084C0A-E0FD-4224-9040-2E57D246F5D6}">
+  <dimension ref="A1:H96"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.1796875" customWidth="1"/>
+    <col min="2" max="2" width="36.08984375" customWidth="1"/>
+    <col min="3" max="3" width="25.6328125" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" customWidth="1"/>
+    <col min="5" max="5" width="32.36328125" customWidth="1"/>
+    <col min="6" max="6" width="36.7265625" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" customWidth="1"/>
+    <col min="8" max="8" width="18.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.45">
+      <c r="A3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="6">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6">
+        <v>31172</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="6">
+        <v>14.92</v>
+      </c>
+      <c r="H7" s="6">
+        <v>410.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6">
+        <v>19</v>
+      </c>
+      <c r="E8" s="6">
+        <v>12565</v>
+      </c>
+      <c r="F8" s="6">
+        <v>94.7</v>
+      </c>
+      <c r="G8" s="6">
+        <v>13.69</v>
+      </c>
+      <c r="H8" s="6">
+        <v>165.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6">
+        <v>19</v>
+      </c>
+      <c r="E9" s="6">
+        <v>5244</v>
+      </c>
+      <c r="F9" s="6">
+        <v>94.7</v>
+      </c>
+      <c r="G9" s="6">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="H9" s="6">
+        <v>69.099999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="6">
+        <v>19</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2723</v>
+      </c>
+      <c r="F10" s="6">
+        <v>84.2</v>
+      </c>
+      <c r="G10" s="6">
+        <v>2.42</v>
+      </c>
+      <c r="H10" s="6">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="6">
+        <v>19</v>
+      </c>
+      <c r="E11" s="6">
+        <v>742</v>
+      </c>
+      <c r="F11" s="6">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1.31</v>
+      </c>
+      <c r="H11" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="6">
+        <v>19</v>
+      </c>
+      <c r="E12" s="6">
+        <v>208</v>
+      </c>
+      <c r="F12" s="6">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.78</v>
+      </c>
+      <c r="H12" s="6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="6">
+        <v>17</v>
+      </c>
+      <c r="E13" s="6">
+        <v>34272</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="6">
+        <v>11.35</v>
+      </c>
+      <c r="H13" s="6">
+        <v>451.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="6">
+        <v>17</v>
+      </c>
+      <c r="E14" s="6">
+        <v>14713</v>
+      </c>
+      <c r="F14" s="6">
+        <v>76.5</v>
+      </c>
+      <c r="G14" s="6">
+        <v>7.16</v>
+      </c>
+      <c r="H14" s="6">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="6">
+        <v>17</v>
+      </c>
+      <c r="E15" s="6">
+        <v>6512</v>
+      </c>
+      <c r="F15" s="6">
+        <v>76.5</v>
+      </c>
+      <c r="G15" s="6">
+        <v>2.02</v>
+      </c>
+      <c r="H15" s="6">
+        <v>85.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6">
+        <v>17</v>
+      </c>
+      <c r="E16" s="6">
+        <v>3288</v>
+      </c>
+      <c r="F16" s="6">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="G16" s="6">
+        <v>2.08</v>
+      </c>
+      <c r="H16" s="6">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="6">
+        <v>17</v>
+      </c>
+      <c r="E17" s="6">
+        <v>822</v>
+      </c>
+      <c r="F17" s="6">
+        <v>52.9</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H17" s="6">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="6">
+        <v>17</v>
+      </c>
+      <c r="E18" s="6">
+        <v>197</v>
+      </c>
+      <c r="F18" s="6">
+        <v>11.8</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1.27</v>
+      </c>
+      <c r="H18" s="6">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="6">
+        <v>17</v>
+      </c>
+      <c r="E19" s="6">
+        <v>39423</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="6">
+        <v>13.14</v>
+      </c>
+      <c r="H19" s="6">
+        <v>519.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="6">
+        <v>17</v>
+      </c>
+      <c r="E20" s="6">
+        <v>15568</v>
+      </c>
+      <c r="F20" s="6">
+        <v>100</v>
+      </c>
+      <c r="G20" s="6">
+        <v>7.82</v>
+      </c>
+      <c r="H20" s="6">
+        <v>205.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="6">
+        <v>17</v>
+      </c>
+      <c r="E21" s="6">
+        <v>6650</v>
+      </c>
+      <c r="F21" s="6">
+        <v>100</v>
+      </c>
+      <c r="G21" s="6">
+        <v>4.91</v>
+      </c>
+      <c r="H21" s="6">
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="6">
+        <v>17</v>
+      </c>
+      <c r="E22" s="6">
+        <v>3264</v>
+      </c>
+      <c r="F22" s="6">
+        <v>88.2</v>
+      </c>
+      <c r="G22" s="6">
+        <v>2.84</v>
+      </c>
+      <c r="H22" s="6">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="6">
+        <v>17</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1014</v>
+      </c>
+      <c r="F23" s="6">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1.28</v>
+      </c>
+      <c r="H23" s="6">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="6">
+        <v>17</v>
+      </c>
+      <c r="E24" s="6">
+        <v>349</v>
+      </c>
+      <c r="F24" s="6">
+        <v>47.1</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="H24" s="6">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="6">
+        <v>20</v>
+      </c>
+      <c r="E25" s="6">
+        <v>22915</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="6">
+        <v>12.65</v>
+      </c>
+      <c r="H25" s="6">
+        <v>301.89999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="6">
+        <v>20</v>
+      </c>
+      <c r="E26" s="6">
+        <v>7870</v>
+      </c>
+      <c r="F26" s="6">
+        <v>45</v>
+      </c>
+      <c r="G26" s="6">
+        <v>3.29</v>
+      </c>
+      <c r="H26" s="6">
+        <v>103.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="6">
+        <v>20</v>
+      </c>
+      <c r="E27" s="6">
+        <v>3633</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="6">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="6">
+        <v>20</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1949</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="6">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="6">
+        <v>20</v>
+      </c>
+      <c r="E29" s="6">
+        <v>768</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="6">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="6">
+        <v>20</v>
+      </c>
+      <c r="E30" s="6">
+        <v>248</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="6">
+        <v>23</v>
+      </c>
+      <c r="E31" s="6">
+        <v>28297</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="6">
+        <v>20.53</v>
+      </c>
+      <c r="H31" s="6">
+        <v>372.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="6">
+        <v>23</v>
+      </c>
+      <c r="E32" s="6">
+        <v>15182</v>
+      </c>
+      <c r="F32" s="6">
+        <v>39.1</v>
+      </c>
+      <c r="G32" s="6">
+        <v>14.46</v>
+      </c>
+      <c r="H32" s="6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="6">
+        <v>23</v>
+      </c>
+      <c r="E33" s="6">
+        <v>5224</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="6">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="6">
+        <v>23</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1602</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="6">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="6">
+        <v>23</v>
+      </c>
+      <c r="E35" s="6">
+        <v>626</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="6">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="6">
+        <v>23</v>
+      </c>
+      <c r="E36" s="6">
+        <v>168</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="6">
+        <v>40</v>
+      </c>
+      <c r="E37" s="6">
+        <v>164533</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" s="6">
+        <v>20.79</v>
+      </c>
+      <c r="H37" s="6">
+        <v>2103.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="6">
+        <v>40</v>
+      </c>
+      <c r="E38" s="6">
+        <v>49785</v>
+      </c>
+      <c r="F38" s="6">
+        <v>95</v>
+      </c>
+      <c r="G38" s="6">
+        <v>11.7</v>
+      </c>
+      <c r="H38" s="6">
+        <v>636.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="6">
+        <v>40</v>
+      </c>
+      <c r="E39" s="6">
+        <v>14654</v>
+      </c>
+      <c r="F39" s="6">
+        <v>75</v>
+      </c>
+      <c r="G39" s="6">
+        <v>5.24</v>
+      </c>
+      <c r="H39" s="6">
+        <v>187.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="6">
+        <v>40</v>
+      </c>
+      <c r="E40" s="6">
+        <v>4929</v>
+      </c>
+      <c r="F40" s="6">
+        <v>57.5</v>
+      </c>
+      <c r="G40" s="6">
+        <v>3.23</v>
+      </c>
+      <c r="H40" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="6">
+        <v>40</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1393</v>
+      </c>
+      <c r="F41" s="6">
+        <v>27.5</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="H41" s="6">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="6">
+        <v>40</v>
+      </c>
+      <c r="E42" s="6">
+        <v>327</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="6">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="6">
+        <v>40</v>
+      </c>
+      <c r="E43" s="6">
+        <v>141581</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G43" s="6">
+        <v>19</v>
+      </c>
+      <c r="H43" s="6">
+        <v>1809.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="6">
+        <v>40</v>
+      </c>
+      <c r="E44" s="6">
+        <v>42920</v>
+      </c>
+      <c r="F44" s="6">
+        <v>100</v>
+      </c>
+      <c r="G44" s="6">
+        <v>9.17</v>
+      </c>
+      <c r="H44" s="6">
+        <v>548.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="6">
+        <v>40</v>
+      </c>
+      <c r="E45" s="6">
+        <v>13625</v>
+      </c>
+      <c r="F45" s="6">
+        <v>85</v>
+      </c>
+      <c r="G45" s="6">
+        <v>4.53</v>
+      </c>
+      <c r="H45" s="6">
+        <v>174.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="6">
+        <v>40</v>
+      </c>
+      <c r="E46" s="6">
+        <v>4622</v>
+      </c>
+      <c r="F46" s="6">
+        <v>80</v>
+      </c>
+      <c r="G46" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H46" s="6">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="6">
+        <v>40</v>
+      </c>
+      <c r="E47" s="6">
+        <v>1169</v>
+      </c>
+      <c r="F47" s="6">
+        <v>67.5</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="H47" s="6">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="6">
+        <v>40</v>
+      </c>
+      <c r="E48" s="6">
+        <v>258</v>
+      </c>
+      <c r="F48" s="6">
+        <v>52.5</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="H48" s="6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="6">
+        <v>41</v>
+      </c>
+      <c r="E49" s="6">
+        <v>144481</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G49" s="6">
+        <v>14.99</v>
+      </c>
+      <c r="H49" s="6">
+        <v>1846.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="6">
+        <v>41</v>
+      </c>
+      <c r="E50" s="6">
+        <v>44585</v>
+      </c>
+      <c r="F50" s="6">
+        <v>100</v>
+      </c>
+      <c r="G50" s="6">
+        <v>7.9</v>
+      </c>
+      <c r="H50" s="6">
+        <v>569.9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="6">
+        <v>41</v>
+      </c>
+      <c r="E51" s="6">
+        <v>14560</v>
+      </c>
+      <c r="F51" s="6">
+        <v>95.1</v>
+      </c>
+      <c r="G51" s="6">
+        <v>5.77</v>
+      </c>
+      <c r="H51" s="6">
+        <v>186.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="6">
+        <v>41</v>
+      </c>
+      <c r="E52" s="6">
+        <v>4788</v>
+      </c>
+      <c r="F52" s="6">
+        <v>85.4</v>
+      </c>
+      <c r="G52" s="6">
+        <v>3.47</v>
+      </c>
+      <c r="H52" s="6">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="6">
+        <v>41</v>
+      </c>
+      <c r="E53" s="6">
+        <v>1491</v>
+      </c>
+      <c r="F53" s="6">
+        <v>68.3</v>
+      </c>
+      <c r="G53" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="H53" s="6">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="6">
+        <v>41</v>
+      </c>
+      <c r="E54" s="6">
+        <v>321</v>
+      </c>
+      <c r="F54" s="6">
+        <v>56.1</v>
+      </c>
+      <c r="G54" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="H54" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="6">
+        <v>41</v>
+      </c>
+      <c r="E55" s="6">
+        <v>162924</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" s="6">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="H55" s="6">
+        <v>2082.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="6">
+        <v>41</v>
+      </c>
+      <c r="E56" s="6">
+        <v>55050</v>
+      </c>
+      <c r="F56" s="6">
+        <v>97.6</v>
+      </c>
+      <c r="G56" s="6">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="H56" s="6">
+        <v>703.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="6">
+        <v>41</v>
+      </c>
+      <c r="E57" s="6">
+        <v>17426</v>
+      </c>
+      <c r="F57" s="6">
+        <v>90.2</v>
+      </c>
+      <c r="G57" s="6">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H57" s="6">
+        <v>222.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" s="6">
+        <v>41</v>
+      </c>
+      <c r="E58" s="6">
+        <v>4911</v>
+      </c>
+      <c r="F58" s="6">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="G58" s="6">
+        <v>1.76</v>
+      </c>
+      <c r="H58" s="6">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" s="6">
+        <v>41</v>
+      </c>
+      <c r="E59" s="6">
+        <v>1540</v>
+      </c>
+      <c r="F59" s="6">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="G59" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="H59" s="6">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="6">
+        <v>41</v>
+      </c>
+      <c r="E60" s="6">
+        <v>339</v>
+      </c>
+      <c r="F60" s="6">
+        <v>34.1</v>
+      </c>
+      <c r="G60" s="6">
+        <v>0.64</v>
+      </c>
+      <c r="H60" s="6">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="6">
+        <v>43</v>
+      </c>
+      <c r="E61" s="6">
+        <v>165627</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="6">
+        <v>33.4</v>
+      </c>
+      <c r="H61" s="6">
+        <v>2117.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="6">
+        <v>43</v>
+      </c>
+      <c r="E62" s="6">
+        <v>51820</v>
+      </c>
+      <c r="F62" s="6">
+        <v>90.7</v>
+      </c>
+      <c r="G62" s="6">
+        <v>18.78</v>
+      </c>
+      <c r="H62" s="6">
+        <v>662.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="6">
+        <v>43</v>
+      </c>
+      <c r="E63" s="6">
+        <v>16637</v>
+      </c>
+      <c r="F63" s="6">
+        <v>76.7</v>
+      </c>
+      <c r="G63" s="6">
+        <v>7.05</v>
+      </c>
+      <c r="H63" s="6">
+        <v>212.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="6">
+        <v>43</v>
+      </c>
+      <c r="E64" s="6">
+        <v>4780</v>
+      </c>
+      <c r="F64" s="6">
+        <v>55.8</v>
+      </c>
+      <c r="G64" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="H64" s="6">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" s="6">
+        <v>43</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1424</v>
+      </c>
+      <c r="F65" s="6">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="G65" s="6">
+        <v>1.69</v>
+      </c>
+      <c r="H65" s="6">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" s="6">
+        <v>43</v>
+      </c>
+      <c r="E66" s="6">
+        <v>320</v>
+      </c>
+      <c r="F66" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G66" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="H66" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="6">
+        <v>27</v>
+      </c>
+      <c r="E67" s="6">
+        <v>84326</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G67" s="6">
+        <v>24.14</v>
+      </c>
+      <c r="H67" s="6">
+        <v>1132.9000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="6">
+        <v>27</v>
+      </c>
+      <c r="E68" s="6">
+        <v>11340</v>
+      </c>
+      <c r="F68" s="6">
+        <v>96.3</v>
+      </c>
+      <c r="G68" s="6">
+        <v>11.53</v>
+      </c>
+      <c r="H68" s="6">
+        <v>152.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="6">
+        <v>27</v>
+      </c>
+      <c r="E69" s="6">
+        <v>3969</v>
+      </c>
+      <c r="F69" s="6">
+        <v>92.6</v>
+      </c>
+      <c r="G69" s="6">
+        <v>5.19</v>
+      </c>
+      <c r="H69" s="6">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" s="6">
+        <v>27</v>
+      </c>
+      <c r="E70" s="6">
+        <v>2420</v>
+      </c>
+      <c r="F70" s="6">
+        <v>88.9</v>
+      </c>
+      <c r="G70" s="6">
+        <v>3.14</v>
+      </c>
+      <c r="H70" s="6">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71" s="6">
+        <v>27</v>
+      </c>
+      <c r="E71" s="6">
+        <v>734</v>
+      </c>
+      <c r="F71" s="6">
+        <v>77.8</v>
+      </c>
+      <c r="G71" s="6">
+        <v>1.43</v>
+      </c>
+      <c r="H71" s="6">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" s="6">
+        <v>27</v>
+      </c>
+      <c r="E72" s="6">
+        <v>172</v>
+      </c>
+      <c r="F72" s="6">
+        <v>44.4</v>
+      </c>
+      <c r="G72" s="6">
+        <v>0.81</v>
+      </c>
+      <c r="H72" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="6">
+        <v>25</v>
+      </c>
+      <c r="E73" s="6">
+        <v>79823</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G73" s="6">
+        <v>38.44</v>
+      </c>
+      <c r="H73" s="6">
+        <v>1072.4000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A74" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="6">
+        <v>25</v>
+      </c>
+      <c r="E74" s="6">
+        <v>10865</v>
+      </c>
+      <c r="F74" s="6">
+        <v>96</v>
+      </c>
+      <c r="G74" s="6">
+        <v>18.75</v>
+      </c>
+      <c r="H74" s="6">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="6">
+        <v>25</v>
+      </c>
+      <c r="E75" s="6">
+        <v>4349</v>
+      </c>
+      <c r="F75" s="6">
+        <v>84</v>
+      </c>
+      <c r="G75" s="6">
+        <v>7.04</v>
+      </c>
+      <c r="H75" s="6">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="6">
+        <v>25</v>
+      </c>
+      <c r="E76" s="6">
+        <v>2418</v>
+      </c>
+      <c r="F76" s="6">
+        <v>80</v>
+      </c>
+      <c r="G76" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="H76" s="6">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A77" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" s="6">
+        <v>25</v>
+      </c>
+      <c r="E77" s="6">
+        <v>746</v>
+      </c>
+      <c r="F77" s="6">
+        <v>76</v>
+      </c>
+      <c r="G77" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="H77" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" s="6">
+        <v>25</v>
+      </c>
+      <c r="E78" s="6">
+        <v>246</v>
+      </c>
+      <c r="F78" s="6">
+        <v>56</v>
+      </c>
+      <c r="G78" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="H78" s="6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="6">
+        <v>25</v>
+      </c>
+      <c r="E79" s="6">
+        <v>118615</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G79" s="6">
+        <v>37.75</v>
+      </c>
+      <c r="H79" s="6">
+        <v>1593.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" s="6">
+        <v>25</v>
+      </c>
+      <c r="E80" s="6">
+        <v>18151</v>
+      </c>
+      <c r="F80" s="6">
+        <v>84</v>
+      </c>
+      <c r="G80" s="6">
+        <v>14.17</v>
+      </c>
+      <c r="H80" s="6">
+        <v>243.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" s="6">
+        <v>25</v>
+      </c>
+      <c r="E81" s="6">
+        <v>5511</v>
+      </c>
+      <c r="F81" s="6">
+        <v>76</v>
+      </c>
+      <c r="G81" s="6">
+        <v>6</v>
+      </c>
+      <c r="H81" s="6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" s="6">
+        <v>25</v>
+      </c>
+      <c r="E82" s="6">
+        <v>3177</v>
+      </c>
+      <c r="F82" s="6">
+        <v>56</v>
+      </c>
+      <c r="G82" s="6">
+        <v>2.96</v>
+      </c>
+      <c r="H82" s="6">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" s="6">
+        <v>25</v>
+      </c>
+      <c r="E83" s="6">
+        <v>1029</v>
+      </c>
+      <c r="F83" s="6">
+        <v>48</v>
+      </c>
+      <c r="G83" s="6">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="H83" s="6">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84" s="6">
+        <v>25</v>
+      </c>
+      <c r="E84" s="6">
+        <v>293</v>
+      </c>
+      <c r="F84" s="6">
+        <v>28</v>
+      </c>
+      <c r="G84" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="H84" s="6">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="6">
+        <v>24</v>
+      </c>
+      <c r="E85" s="6">
+        <v>55778</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G85" s="6">
+        <v>21.29</v>
+      </c>
+      <c r="H85" s="6">
+        <v>749.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D86" s="6">
+        <v>24</v>
+      </c>
+      <c r="E86" s="6">
+        <v>5746</v>
+      </c>
+      <c r="F86" s="6">
+        <v>70.8</v>
+      </c>
+      <c r="G86" s="6">
+        <v>12.62</v>
+      </c>
+      <c r="H86" s="6">
+        <v>77.2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" s="6">
+        <v>24</v>
+      </c>
+      <c r="E87" s="6">
+        <v>1940</v>
+      </c>
+      <c r="F87" s="6">
+        <v>54.2</v>
+      </c>
+      <c r="G87" s="6">
+        <v>6.05</v>
+      </c>
+      <c r="H87" s="6">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="6">
+        <v>24</v>
+      </c>
+      <c r="E88" s="6">
+        <v>500</v>
+      </c>
+      <c r="F88" s="6">
+        <v>37.5</v>
+      </c>
+      <c r="G88" s="6">
+        <v>2.54</v>
+      </c>
+      <c r="H88" s="6">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D89" s="6">
+        <v>24</v>
+      </c>
+      <c r="E89" s="6">
+        <v>15</v>
+      </c>
+      <c r="F89" s="6">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H89" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" s="6">
+        <v>24</v>
+      </c>
+      <c r="E90" s="6">
+        <v>4</v>
+      </c>
+      <c r="F90" s="6">
+        <v>0</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="6">
+        <v>25</v>
+      </c>
+      <c r="E91" s="6">
+        <v>98318</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G91" s="6">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="H91" s="6">
+        <v>1320.9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" s="6">
+        <v>25</v>
+      </c>
+      <c r="E92" s="6">
+        <v>16378</v>
+      </c>
+      <c r="F92" s="6">
+        <v>72</v>
+      </c>
+      <c r="G92" s="6">
+        <v>6.11</v>
+      </c>
+      <c r="H92" s="6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D93" s="6">
+        <v>25</v>
+      </c>
+      <c r="E93" s="6">
+        <v>4829</v>
+      </c>
+      <c r="F93" s="6">
+        <v>40</v>
+      </c>
+      <c r="G93" s="6">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="H93" s="6">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D94" s="6">
+        <v>25</v>
+      </c>
+      <c r="E94" s="6">
+        <v>1142</v>
+      </c>
+      <c r="F94" s="6">
+        <v>16</v>
+      </c>
+      <c r="G94" s="6">
+        <v>2.68</v>
+      </c>
+      <c r="H94" s="6">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95" s="6">
+        <v>25</v>
+      </c>
+      <c r="E95" s="6">
+        <v>274</v>
+      </c>
+      <c r="F95" s="6">
+        <v>0</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H95" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D96" s="6">
+        <v>25</v>
+      </c>
+      <c r="E96" s="6">
+        <v>63</v>
+      </c>
+      <c r="F96" s="6">
+        <v>0</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
